--- a/города.xlsx
+++ b/города.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrypotekhin/Downloads/dmpotekhin.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89C037A-CB0E-594E-9C45-E1A248FB4C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B335BA-5227-3D4F-A3D7-7503F59DDDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="520" windowWidth="25040" windowHeight="14900" xr2:uid="{DC266A2C-F39F-6149-B5CF-D2B11DD9043D}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t>Нара</t>
   </si>
@@ -804,6 +804,9 @@
   </si>
   <si>
     <t>Сьюдад-дель-Эсте</t>
+  </si>
+  <si>
+    <t>Мельбурн</t>
   </si>
 </sst>
 </file>
@@ -821,6 +824,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -828,6 +832,7 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1178,7 +1183,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C256"/>
+  <dimension ref="A1:C257"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.19921875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.19921875" customWidth="1"/>
@@ -2467,6 +2472,11 @@
         <v>256</v>
       </c>
     </row>
+    <row r="257" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C1" r:id="rId1" xr:uid="{62D7D27A-D0FF-5241-A9D3-8A4AF319C2A7}"/>
